--- a/Morosos/morosos_listado.xlsx
+++ b/Morosos/morosos_listado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="85">
   <si>
     <t>Nombre estudiante</t>
   </si>
@@ -25,106 +25,220 @@
     <t>grado</t>
   </si>
   <si>
-    <t>Carmona Taborda Luciana</t>
-  </si>
-  <si>
-    <t>Tenorio Maya Liam</t>
-  </si>
-  <si>
-    <t>Fonseca Rivera Emily Sofia</t>
+    <t>Rojas Jimenez Sofia</t>
+  </si>
+  <si>
+    <t>Sanabria Cardona Santiago</t>
+  </si>
+  <si>
+    <t>Segura Rios Samuel Felipe</t>
+  </si>
+  <si>
+    <t>Muñoz Vellojin Mateo</t>
+  </si>
+  <si>
+    <t>Manco Fonnegra Samuel</t>
+  </si>
+  <si>
+    <t>Jaramillo Agudelo Ana Sofia</t>
+  </si>
+  <si>
+    <t>De Luquez Bernal Mabel Sarai</t>
+  </si>
+  <si>
+    <t>Machado Taborda Mateo</t>
+  </si>
+  <si>
+    <t>Mendoza Alvarez Abigail</t>
+  </si>
+  <si>
+    <t>Cortes Correa Rebeca</t>
+  </si>
+  <si>
+    <t>Mariaca Montagut Maria Clara</t>
+  </si>
+  <si>
+    <t>Pérez Hernández Salomé</t>
+  </si>
+  <si>
+    <t>Sayago Acevedo Samuel</t>
+  </si>
+  <si>
+    <t>Troya Rendon Emanuel</t>
   </si>
   <si>
     <t>Ruiz Estrada Sofia Camila</t>
   </si>
   <si>
-    <t>Ruiz Rodas Jacobo</t>
+    <t>Cortes Correa Salome</t>
+  </si>
+  <si>
+    <t>Castaño Viloria Sara</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Juan Martin</t>
+  </si>
+  <si>
+    <t>Hurtado Hurtado Sara</t>
+  </si>
+  <si>
+    <t>Vanegas Pulgarin Sheray</t>
+  </si>
+  <si>
+    <t>Vanegas Olaya Simon</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Roxana</t>
   </si>
   <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
-    <t>Santos Paz Ezra Wolf</t>
-  </si>
-  <si>
-    <t>Marquez Mora Emilia</t>
+    <t>Orrego Jimenez Benjamin</t>
+  </si>
+  <si>
+    <t>Suarez Bayona Martina</t>
+  </si>
+  <si>
+    <t>Cuervo Consuegra Tamara</t>
+  </si>
+  <si>
+    <t>Martinez Alvarez Thiago</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Isaac</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Nicolas</t>
+  </si>
+  <si>
+    <t>Clavijo Quiceno Sara</t>
+  </si>
+  <si>
+    <t>Prieto Albán Mathías</t>
+  </si>
+  <si>
+    <t>Segura Rios Emmanuel David</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Maria Juliana</t>
+  </si>
+  <si>
+    <t>Martinez Ciro Josue</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Simon</t>
   </si>
   <si>
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
-    <t>Zambrano Mejia Mariangel</t>
-  </si>
-  <si>
-    <t>Agudelo Luciana</t>
-  </si>
-  <si>
-    <t>Quintero Suarez Andres David</t>
-  </si>
-  <si>
-    <t>Garcia Correa Andres Esteban</t>
-  </si>
-  <si>
-    <t>Sayago Acevedo Samuel</t>
-  </si>
-  <si>
-    <t>Troya Rendon Emanuel</t>
-  </si>
-  <si>
-    <t>Gomez Leon Mateo</t>
-  </si>
-  <si>
-    <t>Ospina Cifuentes Antonella</t>
-  </si>
-  <si>
-    <t>Correa Claudia Patricia</t>
-  </si>
-  <si>
-    <t>Marin Osorio Johny Alexander</t>
-  </si>
-  <si>
-    <t>David Mercado Andres Felipe</t>
+    <t>Prieto Albán Isaac</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Analucia</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Thomás</t>
+  </si>
+  <si>
+    <t>Marino Millan Yelitza Rossana</t>
+  </si>
+  <si>
+    <t>Sanabria Ballen Andres Leonardo</t>
+  </si>
+  <si>
+    <t>Segura Camacho Oscar Dario</t>
+  </si>
+  <si>
+    <t>Vellojin Cavadia Tania Marjolia</t>
+  </si>
+  <si>
+    <t>Manco Echavarria Reynel De Jesus</t>
+  </si>
+  <si>
+    <t>Agudelo Torres Sumilde Elena</t>
+  </si>
+  <si>
+    <t>De Luquez Diaz Ezequiel</t>
+  </si>
+  <si>
+    <t>Sas Inversiones Myt</t>
+  </si>
+  <si>
+    <t>Alvarez Martinez Glenys Yanet</t>
+  </si>
+  <si>
+    <t>Cortes Velasquez Juan Pablo</t>
+  </si>
+  <si>
+    <t>Montagut Ortiz Clariveth</t>
+  </si>
+  <si>
+    <t>Hernandez Cardona Mauricio</t>
+  </si>
+  <si>
+    <t>Acevedo Galeano Viviana</t>
+  </si>
+  <si>
+    <t>Troya Osorio Manuel Enrique</t>
   </si>
   <si>
     <t>Estrada Colon Yerica Del Carmen</t>
   </si>
   <si>
-    <t>Rodas Marin Monica Janeth</t>
+    <t>Viloria Montoya Isabel Cristina</t>
+  </si>
+  <si>
+    <t>Hernandez Baron Lina Paola</t>
+  </si>
+  <si>
+    <t>Hurtado Orozco Yudi Andrea</t>
+  </si>
+  <si>
+    <t>Vanegas Zuñiga Ray Andres</t>
+  </si>
+  <si>
+    <t>Olaya Rojas Liliana Maria</t>
+  </si>
+  <si>
+    <t>Mosquera Rodriguez Tania Karina</t>
   </si>
   <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
-    <t>Santos Lopez Sebastian</t>
-  </si>
-  <si>
-    <t>Mora Cardona Katherine</t>
+    <t>Orrego Zuluaga Juan Esteban</t>
+  </si>
+  <si>
+    <t>Bayona Buitrago Sandra Milena</t>
+  </si>
+  <si>
+    <t>Cuervo Paternina Eder Andres</t>
+  </si>
+  <si>
+    <t>Hernandez Morelo Liliana</t>
+  </si>
+  <si>
+    <t>Ramirez Suarez Leidy Tatiana</t>
+  </si>
+  <si>
+    <t>Carreño Bohorquez Nora Maria</t>
+  </si>
+  <si>
+    <t>Prieto Oyaga Cristhian Camilo</t>
+  </si>
+  <si>
+    <t>Martinez Moreno Devinson</t>
+  </si>
+  <si>
+    <t>Ortiz Velez Laura Catalina</t>
   </si>
   <si>
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
-    <t>Santana Marulanda Stuart</t>
-  </si>
-  <si>
-    <t>Agudelo Juliet Cristina</t>
-  </si>
-  <si>
-    <t>Quintero Gerardino Jairo Andres</t>
-  </si>
-  <si>
-    <t>Correa Osorio Luisa Fernanda</t>
-  </si>
-  <si>
-    <t>Acevedo Galeano Viviana</t>
-  </si>
-  <si>
-    <t>Troya Osorio Manuel Enrique</t>
-  </si>
-  <si>
-    <t>Gomez Serna Daniel</t>
-  </si>
-  <si>
-    <t>Ospina Escobar Nilson James</t>
+    <t>Garcia Valencia Cesar Augusto</t>
   </si>
   <si>
     <t>CUARTO</t>
@@ -133,7 +247,16 @@
     <t>DÉCIMO</t>
   </si>
   <si>
-    <t>PRIMERO</t>
+    <t>NOVENO</t>
+  </si>
+  <si>
+    <t>OCTAVO</t>
+  </si>
+  <si>
+    <t>ONCE</t>
+  </si>
+  <si>
+    <t>QUINTO</t>
   </si>
   <si>
     <t>SEGUNDO</t>
@@ -503,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -522,10 +645,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -533,10 +656,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -544,10 +667,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -555,10 +678,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -566,10 +689,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -577,10 +700,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -588,10 +711,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -599,10 +722,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -610,10 +733,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -621,10 +744,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -632,10 +755,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -643,10 +766,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -654,10 +777,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -665,10 +788,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -676,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -687,10 +810,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -698,10 +821,252 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
-        <v>43</v>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Morosos/morosos_listado.xlsx
+++ b/Morosos/morosos_listado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="471">
   <si>
     <t>Nombre estudiante</t>
   </si>
@@ -25,220 +25,1372 @@
     <t>grado</t>
   </si>
   <si>
+    <t>Ortega Zabala Abigail</t>
+  </si>
+  <si>
+    <t>Rodriguez Posada Violeta</t>
+  </si>
+  <si>
+    <t>Rodriguez Herrera Joaquin</t>
+  </si>
+  <si>
+    <t>Pineda Perez Emily Marian</t>
+  </si>
+  <si>
+    <t>Perez Pino Susana</t>
+  </si>
+  <si>
+    <t>Zorrilla Jaramillo Santiago</t>
+  </si>
+  <si>
+    <t>Lopez Galvis Samuel De Jesus</t>
+  </si>
+  <si>
     <t>Rojas Jimenez Sofia</t>
   </si>
   <si>
+    <t>Giraldo Avendaño Samuel</t>
+  </si>
+  <si>
+    <t>Chaverra Gomez Rebeca</t>
+  </si>
+  <si>
+    <t>Chavarria Osorio Luna Celeste</t>
+  </si>
+  <si>
+    <t>Atehortua Quintero Simon</t>
+  </si>
+  <si>
+    <t>Alzate Monsalve David</t>
+  </si>
+  <si>
+    <t>Usma Jaramillo Maria Celeste</t>
+  </si>
+  <si>
+    <t>Vera Montoya Markos</t>
+  </si>
+  <si>
+    <t>Gil Betancur Tomas</t>
+  </si>
+  <si>
     <t>Sanabria Cardona Santiago</t>
   </si>
   <si>
+    <t>Arenas Alvarez Sara</t>
+  </si>
+  <si>
+    <t>Villanueva Julio Samuel</t>
+  </si>
+  <si>
+    <t>Vargas Wilches Maria Jose</t>
+  </si>
+  <si>
+    <t>Calle Ortiz Danya</t>
+  </si>
+  <si>
+    <t>Castaño Patiño Juan Jose</t>
+  </si>
+  <si>
+    <t>Correa Castañeda Laura</t>
+  </si>
+  <si>
+    <t>Soler Segura Moises Valentin</t>
+  </si>
+  <si>
+    <t>Serna Ramirez Luciana</t>
+  </si>
+  <si>
     <t>Segura Rios Samuel Felipe</t>
   </si>
   <si>
+    <t>Saldarriaga Aguirre Hannah</t>
+  </si>
+  <si>
+    <t>Ruiz Aristizabal Nicolas</t>
+  </si>
+  <si>
+    <t>Ramirez Avila Daniel</t>
+  </si>
+  <si>
+    <t>Pacheco Giraldo Santiago</t>
+  </si>
+  <si>
+    <t>Ortega Zabala Heri Thomas</t>
+  </si>
+  <si>
     <t>Muñoz Vellojin Mateo</t>
   </si>
   <si>
+    <t>Miranda Florez Mariajose</t>
+  </si>
+  <si>
+    <t>Meneses Jimenez Mariangel</t>
+  </si>
+  <si>
+    <t>Martinez Herrera Luciana</t>
+  </si>
+  <si>
     <t>Manco Fonnegra Samuel</t>
   </si>
   <si>
     <t>Jaramillo Agudelo Ana Sofia</t>
   </si>
   <si>
+    <t>Gonzalez Rodriguez Haniel Adrian</t>
+  </si>
+  <si>
+    <t>Gonzalez Bedoya Juanita</t>
+  </si>
+  <si>
+    <t>Echeverri Agudelo Samuel</t>
+  </si>
+  <si>
+    <t>Diaz Gonzalez Matias</t>
+  </si>
+  <si>
     <t>De Luquez Bernal Mabel Sarai</t>
   </si>
   <si>
+    <t>Torres Jimenez Juan Simon</t>
+  </si>
+  <si>
+    <t>Viloria Quiceno Isaac</t>
+  </si>
+  <si>
+    <t>Villegas Vargas Mariangel</t>
+  </si>
+  <si>
+    <t>Arboleda Bastos Ximena</t>
+  </si>
+  <si>
+    <t>Alvarez Valencia Ana Elisa</t>
+  </si>
+  <si>
+    <t>Cortes Bedoya Susana</t>
+  </si>
+  <si>
+    <t>Betancur Cardona Samuel</t>
+  </si>
+  <si>
+    <t>Baena Rodas Juan Jose</t>
+  </si>
+  <si>
+    <t>Aguirre Gomez Susana</t>
+  </si>
+  <si>
+    <t>Escalante Martinez Samuel</t>
+  </si>
+  <si>
+    <t>Garzon Moreno Cristian</t>
+  </si>
+  <si>
+    <t>Gaviria Cespedes Brenda</t>
+  </si>
+  <si>
+    <t>Giraldo Perez Ana Isabel</t>
+  </si>
+  <si>
+    <t>Lopez Galvis Sofia</t>
+  </si>
+  <si>
+    <t>Luna Rincon Juan Sebastian</t>
+  </si>
+  <si>
     <t>Machado Taborda Mateo</t>
   </si>
   <si>
+    <t>Marin Jaramillo Nicolas</t>
+  </si>
+  <si>
     <t>Mendoza Alvarez Abigail</t>
   </si>
   <si>
+    <t>Ramirez Morales Salome</t>
+  </si>
+  <si>
+    <t>Restrepo Cadavid Emanuel</t>
+  </si>
+  <si>
+    <t>Rios Salazar Santiago</t>
+  </si>
+  <si>
+    <t>Ruiz Urquijo Martin</t>
+  </si>
+  <si>
+    <t>Salazar Bermudez Paulina</t>
+  </si>
+  <si>
+    <t>Sanchez Bustamante Genesis</t>
+  </si>
+  <si>
+    <t>Sanchez Ortega Susana</t>
+  </si>
+  <si>
+    <t>Tamayo Saldarriaga Salome</t>
+  </si>
+  <si>
+    <t>Usuga Hidalgo Juan Sebastian</t>
+  </si>
+  <si>
+    <t>Vanegas Olaya Cristopher</t>
+  </si>
+  <si>
+    <t>Castañeda Gil Valeria</t>
+  </si>
+  <si>
+    <t>Alvarez Cano Elizabeth</t>
+  </si>
+  <si>
+    <t>Echavarria Muñoz Isabella</t>
+  </si>
+  <si>
+    <t>Espinal Giraldo Benjamin</t>
+  </si>
+  <si>
     <t>Cortes Correa Rebeca</t>
   </si>
   <si>
+    <t>Correa Castaño Christopher</t>
+  </si>
+  <si>
+    <t>Garcia Correa Andres Esteban</t>
+  </si>
+  <si>
+    <t>Garro Cuartas Jeronimo</t>
+  </si>
+  <si>
+    <t>Gonzalez Bedoya Gracia</t>
+  </si>
+  <si>
+    <t>Londoño Sanchez Antonia</t>
+  </si>
+  <si>
     <t>Mariaca Montagut Maria Clara</t>
   </si>
   <si>
+    <t>Martinez Herrera Juan Diego</t>
+  </si>
+  <si>
+    <t>Miranda Florez Josue David</t>
+  </si>
+  <si>
+    <t>Ochoa Herrera Sara</t>
+  </si>
+  <si>
     <t>Pérez Hernández Salomé</t>
   </si>
   <si>
+    <t>Piedrahita Betancur Ana Sofia</t>
+  </si>
+  <si>
+    <t>Rincon Medina Emanuel</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Julieta</t>
+  </si>
+  <si>
     <t>Sayago Acevedo Samuel</t>
   </si>
   <si>
+    <t>Sierra Peñaranda Miguel Angel</t>
+  </si>
+  <si>
+    <t>Suescun Yepes Juan Manuel</t>
+  </si>
+  <si>
+    <t>Torres Jimenez Benjamin</t>
+  </si>
+  <si>
     <t>Troya Rendon Emanuel</t>
   </si>
   <si>
+    <t>Zabala Montoya Emiliano</t>
+  </si>
+  <si>
+    <t>Bohorquez Vera Juan Esteban</t>
+  </si>
+  <si>
+    <t>Betancur Zapata Emanuel</t>
+  </si>
+  <si>
+    <t>Arenas Calderon Evoleth</t>
+  </si>
+  <si>
+    <t>Bernal Monroy Daniel Matias</t>
+  </si>
+  <si>
+    <t>Sanchez Bustamante Manuela</t>
+  </si>
+  <si>
+    <t>Suescun Yepes Luciana</t>
+  </si>
+  <si>
+    <t>Riaño Alzate Santiago</t>
+  </si>
+  <si>
+    <t>Castaño Viloria Sara</t>
+  </si>
+  <si>
+    <t>Cortes Correa Salome</t>
+  </si>
+  <si>
+    <t>Garcia Velez Isabella</t>
+  </si>
+  <si>
+    <t>Gomez Buitrago Mariangel</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Ashley Carolina</t>
+  </si>
+  <si>
+    <t>Gutierrez Ciro Sebastian</t>
+  </si>
+  <si>
+    <t>Henao Rua Sara</t>
+  </si>
+  <si>
+    <t>Jaramillo Carranza Santiago</t>
+  </si>
+  <si>
+    <t>Martinez Correa Tomas</t>
+  </si>
+  <si>
+    <t>Ortiz Monsalve Sebastian</t>
+  </si>
+  <si>
+    <t>Ospina Tuberquia Miguel Angel</t>
+  </si>
+  <si>
+    <t>Restrepo Cadavid Isabela</t>
+  </si>
+  <si>
     <t>Ruiz Estrada Sofia Camila</t>
   </si>
   <si>
-    <t>Cortes Correa Salome</t>
-  </si>
-  <si>
-    <t>Castaño Viloria Sara</t>
+    <t>Carvajal Gomez Shari Lined</t>
+  </si>
+  <si>
+    <t>Ruiz Rodas Jacobo</t>
+  </si>
+  <si>
+    <t>Saldarriaga Isaza Ana Sofia</t>
+  </si>
+  <si>
+    <t>Rizo Paez Elisa Victoria</t>
+  </si>
+  <si>
+    <t>Caicedo Martinez Emmanuel</t>
+  </si>
+  <si>
+    <t>Calle Castaño Emmanuel</t>
+  </si>
+  <si>
+    <t>Chavarriaga Quintero Salome</t>
+  </si>
+  <si>
+    <t>Cifuentes Vergara Gabriela</t>
+  </si>
+  <si>
+    <t>Florez Alvarez Juan David</t>
+  </si>
+  <si>
+    <t>Vanegas Cano Matias</t>
+  </si>
+  <si>
+    <t>Gil Betancur Marcos</t>
+  </si>
+  <si>
+    <t>Jarvis Estrada Arya Elowyn</t>
+  </si>
+  <si>
+    <t>León Vergara Jacobo</t>
+  </si>
+  <si>
+    <t>Londoño Jaramillo Samuel</t>
+  </si>
+  <si>
+    <t>Marin Vergara Nicolas</t>
+  </si>
+  <si>
+    <t>Ortiz Cano Sara</t>
+  </si>
+  <si>
+    <t>Granda Jaramillo Agustin</t>
+  </si>
+  <si>
+    <t>Betancur Ortiz Isabella</t>
+  </si>
+  <si>
+    <t>Vanegas Pulgarin Sheray</t>
+  </si>
+  <si>
+    <t>Vanegas Olaya Simon</t>
+  </si>
+  <si>
+    <t>Blandon Barragan Juan David</t>
+  </si>
+  <si>
+    <t>Alvarez Teran Josue</t>
+  </si>
+  <si>
+    <t>Bran Arrieta Saray</t>
+  </si>
+  <si>
+    <t>Atehortua Quintero Miguel Angel</t>
+  </si>
+  <si>
+    <t>Zambrano Blanco Luis Felipe</t>
+  </si>
+  <si>
+    <t>Gonzalez Gamboa Julieta</t>
+  </si>
+  <si>
+    <t>Giraldo Lozano Emma</t>
+  </si>
+  <si>
+    <t>Castaño Ramirez Matias</t>
+  </si>
+  <si>
+    <t>Cardenas Martinez Cristian Mathias</t>
+  </si>
+  <si>
+    <t>Buitrago Caicedo Juan Sebastian</t>
+  </si>
+  <si>
+    <t>Hurtado Hurtado Sara</t>
+  </si>
+  <si>
+    <t>Ibarra Villamil Jose Alejandro</t>
+  </si>
+  <si>
+    <t>Jaramillo Tovio Violeta</t>
+  </si>
+  <si>
+    <t>Marin Orozco Matias</t>
+  </si>
+  <si>
+    <t>Granda Jaramillo Benjamin</t>
+  </si>
+  <si>
+    <t>Ochoa Herrera Michelle</t>
+  </si>
+  <si>
+    <t>Munera Ceballos Isabel</t>
+  </si>
+  <si>
+    <t>Perea Sanchez Maycol Stiven</t>
+  </si>
+  <si>
+    <t>Pineda Alarcon Ismael</t>
+  </si>
+  <si>
+    <t>Posada Alzate Abraham</t>
+  </si>
+  <si>
+    <t>Rizo Paez David Armando</t>
+  </si>
+  <si>
+    <t>Sanchez Peñaranda Hernan Enrique</t>
+  </si>
+  <si>
+    <t>Sauls Peña Joshua</t>
   </si>
   <si>
     <t>Sorza Hernandez Juan Martin</t>
   </si>
   <si>
-    <t>Hurtado Hurtado Sara</t>
-  </si>
-  <si>
-    <t>Vanegas Pulgarin Sheray</t>
-  </si>
-  <si>
-    <t>Vanegas Olaya Simon</t>
+    <t>Tabares Martinez Martina</t>
+  </si>
+  <si>
+    <t>Tamayo Miranda Isabella</t>
+  </si>
+  <si>
+    <t>Tenorio Maya Liam</t>
+  </si>
+  <si>
+    <t>Peña González Sophia</t>
+  </si>
+  <si>
+    <t>Herrera Higuita Antonia</t>
+  </si>
+  <si>
+    <t>Durango Vasco Mara</t>
+  </si>
+  <si>
+    <t>Correa Rios Simón</t>
+  </si>
+  <si>
+    <t>Correa Rios Martin</t>
+  </si>
+  <si>
+    <t>Araque Gomez Samantha</t>
+  </si>
+  <si>
+    <t>Cano Muñoz Agustin</t>
+  </si>
+  <si>
+    <t>Arenas Calderon Salomon</t>
+  </si>
+  <si>
+    <t>Garcia Velez Lucas</t>
+  </si>
+  <si>
+    <t>Aguirre Gomez Ariana</t>
   </si>
   <si>
     <t>Cardona Mosquera Roxana</t>
   </si>
   <si>
+    <t>Hincapie Rosales Jose Ricardo</t>
+  </si>
+  <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
+    <t>Marquez Mora Emilia</t>
+  </si>
+  <si>
+    <t>Moreno Higuita Abigail</t>
+  </si>
+  <si>
+    <t>Ruiz Urquijo Violeta</t>
+  </si>
+  <si>
+    <t>Zapata Echeverry Abigail</t>
+  </si>
+  <si>
+    <t>Marin Arias Juan Jose</t>
+  </si>
+  <si>
+    <t>Perilla Chica Isabella</t>
+  </si>
+  <si>
+    <t>Pernett Tobon David</t>
+  </si>
+  <si>
+    <t>Ramirez Avila Sara</t>
+  </si>
+  <si>
+    <t>Riaño Alzate Felipe</t>
+  </si>
+  <si>
+    <t>Rios Alarcon Valentina</t>
+  </si>
+  <si>
+    <t>Rios Hurtado Miguel Angel</t>
+  </si>
+  <si>
+    <t>Soler Segura Aaron Jeremias</t>
+  </si>
+  <si>
+    <t>Suarez Bayona Martina</t>
+  </si>
+  <si>
     <t>Orrego Jimenez Benjamin</t>
   </si>
   <si>
-    <t>Suarez Bayona Martina</t>
+    <t>Narvaez Martinez Samuel</t>
+  </si>
+  <si>
+    <t>Marin Correa Matias</t>
+  </si>
+  <si>
+    <t>Hurtado Villamarin Violetta</t>
+  </si>
+  <si>
+    <t>Giraldo Cano Emiliano</t>
+  </si>
+  <si>
+    <t>Gallego Ruiz Matias</t>
+  </si>
+  <si>
+    <t>Ferraro Gallego Santiago</t>
+  </si>
+  <si>
+    <t>Escalante Martinez Sara</t>
+  </si>
+  <si>
+    <t>De La Ossa Mejia Micaias</t>
   </si>
   <si>
     <t>Cuervo Consuegra Tamara</t>
   </si>
   <si>
+    <t>Bedoya Arevalo Estefany</t>
+  </si>
+  <si>
+    <t>Ortiz Montoya Matias</t>
+  </si>
+  <si>
     <t>Martinez Alvarez Thiago</t>
   </si>
   <si>
+    <t>Perez Coronado David</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Maria Juliana</t>
+  </si>
+  <si>
+    <t>Segura Rios Emmanuel David</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Simon</t>
+  </si>
+  <si>
+    <t>Balladares Loayza Mathias Alejandro</t>
+  </si>
+  <si>
+    <t>Cano Giraldo Nissi Maria Belen</t>
+  </si>
+  <si>
     <t>Cardona Mosquera Isaac</t>
   </si>
   <si>
+    <t>Clavijo Quiceno Sara</t>
+  </si>
+  <si>
+    <t>Florez Henao Stefany</t>
+  </si>
+  <si>
+    <t>Garcia Arias Jheremy David</t>
+  </si>
+  <si>
+    <t>Garzon Herrera Joel</t>
+  </si>
+  <si>
+    <t>Gonzalez Mora Emily</t>
+  </si>
+  <si>
+    <t>Hoyos Barrera Maximiliano</t>
+  </si>
+  <si>
     <t>Garcia Ramirez Nicolas</t>
   </si>
   <si>
-    <t>Clavijo Quiceno Sara</t>
+    <t>Mariaca Montagut Alejandra</t>
+  </si>
+  <si>
+    <t>Sanchez Otalvaro Guadalupe</t>
+  </si>
+  <si>
+    <t>Jaramillo Carranza Camila</t>
+  </si>
+  <si>
+    <t>Ramirez Ramirez Luciana</t>
   </si>
   <si>
     <t>Prieto Albán Mathías</t>
   </si>
   <si>
-    <t>Segura Rios Emmanuel David</t>
-  </si>
-  <si>
-    <t>Sorza Hernandez Maria Juliana</t>
+    <t>Perez Cortes Sara</t>
+  </si>
+  <si>
+    <t>Sanchez Bustamante Sarah Joann</t>
+  </si>
+  <si>
+    <t>Mesa Cardona Mariangel</t>
   </si>
   <si>
     <t>Martinez Ciro Josue</t>
   </si>
   <si>
-    <t>Velez Ortiz Simon</t>
+    <t>Martinez Alvarez Daniella</t>
+  </si>
+  <si>
+    <t>Montagut Ibañez Sara</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Norah Isabella</t>
+  </si>
+  <si>
+    <t>Alvarez Cano Yerik</t>
+  </si>
+  <si>
+    <t>Alvarez Mancilla David Luiz</t>
+  </si>
+  <si>
+    <t>Caro Soto Samuel</t>
+  </si>
+  <si>
+    <t>Correa Berrio Emiliano</t>
+  </si>
+  <si>
+    <t>Galindez Florez Maria Paz</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Thomás</t>
+  </si>
+  <si>
+    <t>Gaviria Zapata Maria José</t>
+  </si>
+  <si>
+    <t>Henao Pinilla Simon</t>
+  </si>
+  <si>
+    <t>Zambrano Mejia Mariangel</t>
+  </si>
+  <si>
+    <t>Mejia Alvarez Isabella</t>
+  </si>
+  <si>
+    <t>Montoya Serrano Andres</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Analucia</t>
+  </si>
+  <si>
+    <t>Otalora Ramirez Sofia</t>
+  </si>
+  <si>
+    <t>Prieto Albán Isaac</t>
+  </si>
+  <si>
+    <t>Restrepo Cortes Isabella</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Josue</t>
   </si>
   <si>
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
-    <t>Prieto Albán Isaac</t>
-  </si>
-  <si>
-    <t>Orrego Jimenez Analucia</t>
-  </si>
-  <si>
-    <t>Garcia Ramirez Thomás</t>
+    <t>Yepes Murillo Mariangel</t>
+  </si>
+  <si>
+    <t>Londoño Jaramillo Ezequiel</t>
+  </si>
+  <si>
+    <t>Diez Ortega Isaac</t>
+  </si>
+  <si>
+    <t>Bedoya Garcia Juana Valentina</t>
+  </si>
+  <si>
+    <t>Zabala Cuervo Diana Rocio</t>
+  </si>
+  <si>
+    <t>Rodriguez Tejada Arley Humberto</t>
+  </si>
+  <si>
+    <t>Herrera Martinez Claudia Rocio</t>
+  </si>
+  <si>
+    <t>Integrales Sas Areda Consultores</t>
+  </si>
+  <si>
+    <t>Perez Toro Juan Pablo</t>
+  </si>
+  <si>
+    <t>Zorrilla Adarve Oscar Wilfredo</t>
+  </si>
+  <si>
+    <t>Lopez Giraldo Johnnatan De Jesus</t>
   </si>
   <si>
     <t>Marino Millan Yelitza Rossana</t>
   </si>
   <si>
+    <t>Avendaño Tamayo Yudi Patricia</t>
+  </si>
+  <si>
+    <t>Chaverra Chaverra Juan David</t>
+  </si>
+  <si>
+    <t>Chavarria Ramirez Roman Alberto</t>
+  </si>
+  <si>
+    <t>Atehortua Morales Didier</t>
+  </si>
+  <si>
+    <t>Alzate Villa William</t>
+  </si>
+  <si>
+    <t>Usma Acevedo Elkin Humberto</t>
+  </si>
+  <si>
+    <t>Vera Villa Juan Ferney</t>
+  </si>
+  <si>
+    <t>Gil Zabala Andres Felipe</t>
+  </si>
+  <si>
     <t>Sanabria Ballen Andres Leonardo</t>
   </si>
   <si>
+    <t>Arenas Jorge Enrique</t>
+  </si>
+  <si>
+    <t>Villanueva Meza Manuel Ramon</t>
+  </si>
+  <si>
+    <t>Vargas Ramos Ivan Isidro</t>
+  </si>
+  <si>
+    <t>Taborda Uribe Gladys Amparo</t>
+  </si>
+  <si>
+    <t>Castaño Zapata Jose Fernando</t>
+  </si>
+  <si>
+    <t>Correa Correa Mauricio</t>
+  </si>
+  <si>
+    <t>Soler Ruiz Jorge Luis</t>
+  </si>
+  <si>
+    <t>Arboleda Ramirez Daniel Andres</t>
+  </si>
+  <si>
     <t>Segura Camacho Oscar Dario</t>
   </si>
   <si>
+    <t>Claudina Estela Aguirre Diaz</t>
+  </si>
+  <si>
+    <t>Agudelo Ruiz Sergio Mario</t>
+  </si>
+  <si>
+    <t>Ramirez Urrutia Fredy</t>
+  </si>
+  <si>
+    <t>Pacheco Basilio Wiliam</t>
+  </si>
+  <si>
     <t>Vellojin Cavadia Tania Marjolia</t>
   </si>
   <si>
+    <t>Miranda Giraldo David</t>
+  </si>
+  <si>
+    <t>Meneses Schroeder Henry Harold</t>
+  </si>
+  <si>
+    <t>Martínez Ramírez Diego Alexander</t>
+  </si>
+  <si>
     <t>Manco Echavarria Reynel De Jesus</t>
   </si>
   <si>
     <t>Agudelo Torres Sumilde Elena</t>
   </si>
   <si>
+    <t>Rodriguez Rincon Ligia Stella</t>
+  </si>
+  <si>
+    <t>Gonzalez Diaz Mauricio De Jesus</t>
+  </si>
+  <si>
+    <t>Echeverry Agudelo Sara Catalina</t>
+  </si>
+  <si>
+    <t>Diaz Rico John Edwin</t>
+  </si>
+  <si>
     <t>De Luquez Diaz Ezequiel</t>
   </si>
   <si>
+    <t>Torres Lopez Gustavo Adolfo</t>
+  </si>
+  <si>
+    <t>Viloria Montoya Enrique Alexander</t>
+  </si>
+  <si>
+    <t>Villegas Gonzalez Wbeimar Alexander</t>
+  </si>
+  <si>
+    <t>Sanchez Katherine Bastos</t>
+  </si>
+  <si>
+    <t>Alvarez Arbelaez Hector Dario</t>
+  </si>
+  <si>
+    <t>Cortes Palacio John Fernando</t>
+  </si>
+  <si>
+    <t>Cardona Gómez Marcela</t>
+  </si>
+  <si>
+    <t>Baena Alvarez Jorge Alexis</t>
+  </si>
+  <si>
+    <t>Aguirre Naranjo Bryan Stiven</t>
+  </si>
+  <si>
+    <t>Forero Reyes Janeth</t>
+  </si>
+  <si>
+    <t>Garzon Prieto Nelson Fidel</t>
+  </si>
+  <si>
+    <t>Cespedes Restrepo Maria Alejandra</t>
+  </si>
+  <si>
+    <t>Giraldo Hoyos David</t>
+  </si>
+  <si>
+    <t>Rincon Lopera Liliana Maria</t>
+  </si>
+  <si>
     <t>Sas Inversiones Myt</t>
   </si>
   <si>
+    <t>Marin Jaramillo Juan Camilo</t>
+  </si>
+  <si>
     <t>Alvarez Martinez Glenys Yanet</t>
   </si>
   <si>
+    <t>Callejas Acevedo Geovanny</t>
+  </si>
+  <si>
+    <t>Restrepo Duque Jorge Mauricio</t>
+  </si>
+  <si>
+    <t>Rios Echeverri John Walter</t>
+  </si>
+  <si>
+    <t>Ruiz Cardona Pablo Andres</t>
+  </si>
+  <si>
+    <t>Bermudez Valdes Sandra Janneth</t>
+  </si>
+  <si>
+    <t>Zuleta Castrillon Monica Marcela</t>
+  </si>
+  <si>
+    <t>Sanchez Didomenico Yaksen Marliony</t>
+  </si>
+  <si>
+    <t>Saldarriaga Zuluaga Nancy</t>
+  </si>
+  <si>
+    <t>Usuga Sepulveda Henrry</t>
+  </si>
+  <si>
+    <t>Olaya Rojas Liliana Maria</t>
+  </si>
+  <si>
+    <t>Gil Sanchez Marcela</t>
+  </si>
+  <si>
+    <t>Alvarez Velez Victor Alfonso</t>
+  </si>
+  <si>
+    <t>Echavarría Arley Fernando</t>
+  </si>
+  <si>
+    <t>Espinal Ospina Luis Fernando</t>
+  </si>
+  <si>
     <t>Cortes Velasquez Juan Pablo</t>
   </si>
   <si>
+    <t>Correa Santana Edwin Andres</t>
+  </si>
+  <si>
+    <t>Correa Osorio Luisa Fernanda</t>
+  </si>
+  <si>
+    <t>Garro Sanchez Javier Alexander</t>
+  </si>
+  <si>
+    <t>Sanchez Isaura Pilar</t>
+  </si>
+  <si>
     <t>Montagut Ortiz Clariveth</t>
   </si>
   <si>
+    <t>Sas Prosteam</t>
+  </si>
+  <si>
     <t>Hernandez Cardona Mauricio</t>
   </si>
   <si>
+    <t>Betancur Ramirez Gina Marcela</t>
+  </si>
+  <si>
+    <t>Medina Cardona Erika Grisel</t>
+  </si>
+  <si>
+    <t>Rueda Piedrahita Carlos Ariel</t>
+  </si>
+  <si>
     <t>Acevedo Galeano Viviana</t>
   </si>
   <si>
+    <t>Hernandez Ospina Juan Camilo</t>
+  </si>
+  <si>
+    <t>Suescun Gomez Jhony Alexander</t>
+  </si>
+  <si>
     <t>Troya Osorio Manuel Enrique</t>
   </si>
   <si>
+    <t>Zabala Macias Andres Fabian</t>
+  </si>
+  <si>
+    <t>Bohorquez Almeida Cristian</t>
+  </si>
+  <si>
+    <t>Betancur Gomez Henry Alejandro</t>
+  </si>
+  <si>
+    <t>Arenas Villa Harold Alexander</t>
+  </si>
+  <si>
+    <t>Bernal Coronel Camilo Arturo</t>
+  </si>
+  <si>
+    <t>Riaño Ruiz Gabriel Fernando</t>
+  </si>
+  <si>
+    <t>Viloria Montoya Isabel Cristina</t>
+  </si>
+  <si>
+    <t>Velez Tobon Maria Mercedes</t>
+  </si>
+  <si>
+    <t>Gomez Rios Geovanny Arley</t>
+  </si>
+  <si>
+    <t>Ortiz Julio Sirly Dayana</t>
+  </si>
+  <si>
+    <t>Ciro Romero Claudia Yaneth</t>
+  </si>
+  <si>
+    <t>Henao Zuleta Juan Carlos</t>
+  </si>
+  <si>
+    <t>Carranza Ricardo Diana Marcela</t>
+  </si>
+  <si>
+    <t>Correa Mejia Catalina</t>
+  </si>
+  <si>
+    <t>Ortiz Aristizabal Gabriel Jaime</t>
+  </si>
+  <si>
+    <t>Ospina Diaz Carlos Arturo</t>
+  </si>
+  <si>
     <t>Estrada Colon Yerica Del Carmen</t>
   </si>
   <si>
-    <t>Viloria Montoya Isabel Cristina</t>
+    <t>Gomez Montes Jaime William</t>
+  </si>
+  <si>
+    <t>Rodas Marin Monica Janeth</t>
+  </si>
+  <si>
+    <t>Saldarriaga Gonzalez Carlos Mario</t>
+  </si>
+  <si>
+    <t>Rizo Ibanez Jorge Armando</t>
+  </si>
+  <si>
+    <t>Casas Barrera Jazmin Paola</t>
+  </si>
+  <si>
+    <t>Castaño Tascon Lady Johana</t>
+  </si>
+  <si>
+    <t>Quintero Garcia Harvey Leon</t>
+  </si>
+  <si>
+    <t>Cifuentes Botero Gary Pierre</t>
+  </si>
+  <si>
+    <t>Alvarez Cifuentes Jorge William</t>
+  </si>
+  <si>
+    <t>Vanegas Pineda Bladimir</t>
+  </si>
+  <si>
+    <t>Estrada Vargas Susana</t>
+  </si>
+  <si>
+    <t>Vergara Grau Saira Milena</t>
+  </si>
+  <si>
+    <t>Londoño Moreno Andres Felipe</t>
+  </si>
+  <si>
+    <t>Vergara Mejia Sara Valentina</t>
+  </si>
+  <si>
+    <t>Cano Guarin Sandra Milena</t>
+  </si>
+  <si>
+    <t>Jaramillo Gallego Maria Eugenia</t>
+  </si>
+  <si>
+    <t>Ortiz Monsalve Natalia</t>
+  </si>
+  <si>
+    <t>Vanegas Zuñiga Ray Andres</t>
+  </si>
+  <si>
+    <t>Blandon Tangarife Luis Fernando</t>
+  </si>
+  <si>
+    <t>Alvarez Carlos Mario</t>
+  </si>
+  <si>
+    <t>Arrieta Mendoza Liseth</t>
+  </si>
+  <si>
+    <t>Blanco Rincon Diana Margarita</t>
+  </si>
+  <si>
+    <t>Gamboa Melendrez Jeniffer</t>
+  </si>
+  <si>
+    <t>Lozano Mosquera Mariam</t>
+  </si>
+  <si>
+    <t>Ramirez Ortiz Melissa</t>
+  </si>
+  <si>
+    <t>Cardenas Cordero Christian Enrique</t>
+  </si>
+  <si>
+    <t>Buitrago Gonzalez Edison Alexander</t>
+  </si>
+  <si>
+    <t>Hurtado Orozco Yudi Andrea</t>
+  </si>
+  <si>
+    <t>Villamil Hernandez Lauren Katherine</t>
+  </si>
+  <si>
+    <t>Jaramillo Duque Edwin Fernando</t>
+  </si>
+  <si>
+    <t>Marin Bayron Antonio</t>
+  </si>
+  <si>
+    <t>Munera Castro Wylliam Alberto</t>
+  </si>
+  <si>
+    <t>Perea Mosquera Jose Epifanio</t>
+  </si>
+  <si>
+    <t>Alarcon Arias Yenifer</t>
+  </si>
+  <si>
+    <t>Posada Suarez Gabriel Fernando</t>
+  </si>
+  <si>
+    <t>Peña Morales Eliana Patricia</t>
   </si>
   <si>
     <t>Hernandez Baron Lina Paola</t>
   </si>
   <si>
-    <t>Hurtado Orozco Yudi Andrea</t>
-  </si>
-  <si>
-    <t>Vanegas Zuñiga Ray Andres</t>
-  </si>
-  <si>
-    <t>Olaya Rojas Liliana Maria</t>
+    <t>Tabares Vergara Sergio Adrian</t>
+  </si>
+  <si>
+    <t>Tamayo Usuga Jhon Jairo</t>
+  </si>
+  <si>
+    <t>Marin Osorio Johny Alexander</t>
+  </si>
+  <si>
+    <t>Peña Solórzano Francisco Javier</t>
+  </si>
+  <si>
+    <t>Herrera Serna Oscar Alejandro</t>
+  </si>
+  <si>
+    <t>Vasco Ortiz Yeimy Natalia</t>
+  </si>
+  <si>
+    <t>Correa Navarro Rafael Andres</t>
+  </si>
+  <si>
+    <t>Araque Pineda Valeria</t>
+  </si>
+  <si>
+    <t>Muñoz Zapata Yudy Farley</t>
   </si>
   <si>
     <t>Mosquera Rodriguez Tania Karina</t>
   </si>
   <si>
+    <t>Rosales Quintero Yomaira</t>
+  </si>
+  <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
+    <t>Mora Cardona Katherine</t>
+  </si>
+  <si>
+    <t>Moreno Quintero Daniel Alonso</t>
+  </si>
+  <si>
+    <t>Echeverry Giraldo Estefania</t>
+  </si>
+  <si>
+    <t>Marin Ortiz Juan Carlos</t>
+  </si>
+  <si>
+    <t>Perilla Alarcon Elisio</t>
+  </si>
+  <si>
+    <t>Pernett Ruiz Sebastian</t>
+  </si>
+  <si>
+    <t>Rios Rodriguez Carlos Arturo</t>
+  </si>
+  <si>
+    <t>Hurtado Garzon Rosalba</t>
+  </si>
+  <si>
+    <t>Bayona Buitrago Sandra Milena</t>
+  </si>
+  <si>
     <t>Orrego Zuluaga Juan Esteban</t>
   </si>
   <si>
-    <t>Bayona Buitrago Sandra Milena</t>
+    <t>Martinez Florez Yerlys Sadit</t>
+  </si>
+  <si>
+    <t>Correa Arboleda Ana Maria</t>
+  </si>
+  <si>
+    <t>Hurtado Alvarez Jhojan Stiven</t>
+  </si>
+  <si>
+    <t>Cano Molina Sara Crystal</t>
+  </si>
+  <si>
+    <t>Ruiz Jaqueline</t>
+  </si>
+  <si>
+    <t>Ferraro Trejos Diego Gian Franco</t>
+  </si>
+  <si>
+    <t>De La Ossa Mendoza Abel Jesus</t>
   </si>
   <si>
     <t>Cuervo Paternina Eder Andres</t>
   </si>
   <si>
+    <t>Y Esperanza - Cfe Iglesia Centro De Fe</t>
+  </si>
+  <si>
+    <t>Montoya Silva Paula Andrea</t>
+  </si>
+  <si>
     <t>Hernandez Morelo Liliana</t>
   </si>
   <si>
+    <t>Perez Bohorquez Jhon Robert</t>
+  </si>
+  <si>
+    <t>Ortiz Velez Laura Catalina</t>
+  </si>
+  <si>
+    <t>Balladares Campos Luis Alejandro</t>
+  </si>
+  <si>
+    <t>Giraldo Sepulveda Yisel</t>
+  </si>
+  <si>
+    <t>Carreño Bohorquez Nora Maria</t>
+  </si>
+  <si>
+    <t>Florez Sanchez Miguel Angel</t>
+  </si>
+  <si>
+    <t>Garcia Gomez Reinaldo David</t>
+  </si>
+  <si>
+    <t>Garzon Garcia Milton Arley</t>
+  </si>
+  <si>
+    <t>Gonzalez Mora Julieth Marcela</t>
+  </si>
+  <si>
+    <t>Barrera Zapata Alejandra</t>
+  </si>
+  <si>
     <t>Ramirez Suarez Leidy Tatiana</t>
   </si>
   <si>
-    <t>Carreño Bohorquez Nora Maria</t>
+    <t>Sanchez Agudelo Uber Herney</t>
+  </si>
+  <si>
+    <t>Ramirez Puerta Johnnatan</t>
   </si>
   <si>
     <t>Prieto Oyaga Cristhian Camilo</t>
   </si>
   <si>
+    <t>Perez Betancur Luis Geovanny</t>
+  </si>
+  <si>
+    <t>Cardona Gaviria Maribel</t>
+  </si>
+  <si>
     <t>Martinez Moreno Devinson</t>
   </si>
   <si>
-    <t>Ortiz Velez Laura Catalina</t>
+    <t>Montagut Ortiz Adiel</t>
+  </si>
+  <si>
+    <t>Cano Zapata Stefanny</t>
+  </si>
+  <si>
+    <t>Alvarez Hernandez Guillermo Jose</t>
+  </si>
+  <si>
+    <t>Caro Rivas Grovis Yinois</t>
+  </si>
+  <si>
+    <t>Correa Castañeda Luis Fernando</t>
+  </si>
+  <si>
+    <t>Galindez Daza Cristian Fernando</t>
+  </si>
+  <si>
+    <t>Garcia Valencia Cesar Augusto</t>
+  </si>
+  <si>
+    <t>Gaviria Correa Johan Felipe</t>
+  </si>
+  <si>
+    <t>Henao Betancur Jorge Humberto</t>
+  </si>
+  <si>
+    <t>Santana Marulanda Stuart</t>
+  </si>
+  <si>
+    <t>Mejia Carmona Diego Antonio</t>
+  </si>
+  <si>
+    <t>Alvarez Arboleda Blanca Gladys</t>
+  </si>
+  <si>
+    <t>Otalora Padilla Luis Fernando</t>
+  </si>
+  <si>
+    <t>Restrepo Silva Jeison</t>
   </si>
   <si>
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
-    <t>Garcia Valencia Cesar Augusto</t>
+    <t>Yepes Arias Angela Maria</t>
+  </si>
+  <si>
+    <t>Ortega Arcila Adiela Yohana</t>
+  </si>
+  <si>
+    <t>Garcia Payares Luz Mery</t>
   </si>
   <si>
     <t>CUARTO</t>
@@ -256,6 +1408,9 @@
     <t>ONCE</t>
   </si>
   <si>
+    <t>PRIMERO</t>
+  </si>
+  <si>
     <t>QUINTO</t>
   </si>
   <si>
@@ -269,6 +1424,9 @@
   </si>
   <si>
     <t>TERCERO</t>
+  </si>
+  <si>
+    <t>TRANSICIÓN</t>
   </si>
 </sst>
 </file>
@@ -626,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -645,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -656,10 +1814,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -667,10 +1825,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -678,10 +1836,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -689,10 +1847,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -700,10 +1858,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -711,10 +1869,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -722,10 +1880,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -733,10 +1891,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -744,10 +1902,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -755,10 +1913,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -766,10 +1924,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -777,10 +1935,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -788,10 +1946,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>263</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -799,10 +1957,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -810,10 +1968,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -821,10 +1979,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>266</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -832,10 +1990,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -843,10 +2001,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>268</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -854,10 +2012,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -865,10 +2023,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -876,10 +2034,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -887,10 +2045,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -898,10 +2056,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -909,10 +2067,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>274</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -920,10 +2078,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -931,10 +2089,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -942,10 +2100,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>277</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -953,10 +2111,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>278</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -964,10 +2122,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>279</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -975,10 +2133,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -986,10 +2144,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>280</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -997,10 +2155,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>281</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1008,10 +2166,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>282</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1019,10 +2177,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1030,10 +2188,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>284</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1041,10 +2199,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>285</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1052,10 +2210,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>460</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1063,10 +2221,2298 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
+        <v>287</v>
+      </c>
+      <c r="C40" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>289</v>
+      </c>
+      <c r="C42" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>290</v>
+      </c>
+      <c r="C43" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>291</v>
+      </c>
+      <c r="C44" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C49" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>297</v>
+      </c>
+      <c r="C50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
+        <v>299</v>
+      </c>
+      <c r="C52" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" t="s">
+        <v>300</v>
+      </c>
+      <c r="C53" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>301</v>
+      </c>
+      <c r="C54" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>302</v>
+      </c>
+      <c r="C55" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>303</v>
+      </c>
+      <c r="C56" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C57" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C58" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>305</v>
+      </c>
+      <c r="C59" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>306</v>
+      </c>
+      <c r="C60" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>307</v>
+      </c>
+      <c r="C61" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>308</v>
+      </c>
+      <c r="C62" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>309</v>
+      </c>
+      <c r="C63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>310</v>
+      </c>
+      <c r="C64" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>311</v>
+      </c>
+      <c r="C65" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" t="s">
+        <v>312</v>
+      </c>
+      <c r="C66" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>313</v>
+      </c>
+      <c r="C67" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>314</v>
+      </c>
+      <c r="C68" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" t="s">
+        <v>316</v>
+      </c>
+      <c r="C70" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" t="s">
+        <v>317</v>
+      </c>
+      <c r="C71" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" t="s">
+        <v>318</v>
+      </c>
+      <c r="C72" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>74</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B73" t="s">
+        <v>319</v>
+      </c>
+      <c r="C73" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" t="s">
+        <v>320</v>
+      </c>
+      <c r="C74" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C75" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
+        <v>322</v>
+      </c>
+      <c r="C76" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" t="s">
+        <v>323</v>
+      </c>
+      <c r="C77" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
+        <v>324</v>
+      </c>
+      <c r="C78" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
+        <v>287</v>
+      </c>
+      <c r="C80" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" t="s">
+        <v>327</v>
+      </c>
+      <c r="C82" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>84</v>
+      </c>
+      <c r="B83" t="s">
+        <v>283</v>
+      </c>
+      <c r="C83" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" t="s">
+        <v>281</v>
+      </c>
+      <c r="C84" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" t="s">
+        <v>328</v>
+      </c>
+      <c r="C85" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" t="s">
+        <v>329</v>
+      </c>
+      <c r="C86" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" t="s">
+        <v>330</v>
+      </c>
+      <c r="C87" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="s">
+        <v>331</v>
+      </c>
+      <c r="C88" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" t="s">
+        <v>332</v>
+      </c>
+      <c r="C89" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" t="s">
+        <v>333</v>
+      </c>
+      <c r="C90" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" t="s">
+        <v>334</v>
+      </c>
+      <c r="C91" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" t="s">
+        <v>335</v>
+      </c>
+      <c r="C92" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" t="s">
+        <v>291</v>
+      </c>
+      <c r="C93" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" t="s">
+        <v>336</v>
+      </c>
+      <c r="C94" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" t="s">
+        <v>337</v>
+      </c>
+      <c r="C95" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" t="s">
+        <v>338</v>
+      </c>
+      <c r="C96" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>339</v>
+      </c>
+      <c r="C97" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" t="s">
+        <v>340</v>
+      </c>
+      <c r="C98" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" t="s">
+        <v>341</v>
+      </c>
+      <c r="C99" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>313</v>
+      </c>
+      <c r="C100" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" t="s">
+        <v>342</v>
+      </c>
+      <c r="C102" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" t="s">
+        <v>343</v>
+      </c>
+      <c r="C103" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
+        <v>322</v>
+      </c>
+      <c r="C104" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" t="s">
+        <v>344</v>
+      </c>
+      <c r="C105" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" t="s">
+        <v>346</v>
+      </c>
+      <c r="C107" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" t="s">
+        <v>347</v>
+      </c>
+      <c r="C108" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" t="s">
+        <v>348</v>
+      </c>
+      <c r="C109" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" t="s">
+        <v>349</v>
+      </c>
+      <c r="C110" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>350</v>
+      </c>
+      <c r="C111" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>351</v>
+      </c>
+      <c r="C112" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" t="s">
+        <v>352</v>
+      </c>
+      <c r="C113" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" t="s">
+        <v>309</v>
+      </c>
+      <c r="C114" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" t="s">
+        <v>353</v>
+      </c>
+      <c r="C115" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" t="s">
+        <v>354</v>
+      </c>
+      <c r="C116" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" t="s">
+        <v>356</v>
+      </c>
+      <c r="C118" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" t="s">
+        <v>357</v>
+      </c>
+      <c r="C119" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" t="s">
+        <v>358</v>
+      </c>
+      <c r="C120" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" t="s">
+        <v>359</v>
+      </c>
+      <c r="C121" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" t="s">
+        <v>360</v>
+      </c>
+      <c r="C122" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" t="s">
+        <v>361</v>
+      </c>
+      <c r="C123" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" t="s">
+        <v>362</v>
+      </c>
+      <c r="C124" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" t="s">
+        <v>363</v>
+      </c>
+      <c r="C125" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C126" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" t="s">
+        <v>364</v>
+      </c>
+      <c r="C127" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" t="s">
+        <v>365</v>
+      </c>
+      <c r="C128" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="s">
+        <v>366</v>
+      </c>
+      <c r="C129" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" t="s">
+        <v>367</v>
+      </c>
+      <c r="C130" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" t="s">
+        <v>368</v>
+      </c>
+      <c r="C131" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" t="s">
+        <v>369</v>
+      </c>
+      <c r="C132" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133" t="s">
+        <v>370</v>
+      </c>
+      <c r="C133" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" t="s">
+        <v>371</v>
+      </c>
+      <c r="C134" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="s">
+        <v>317</v>
+      </c>
+      <c r="C135" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" t="s">
+        <v>372</v>
+      </c>
+      <c r="C136" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137" t="s">
+        <v>373</v>
+      </c>
+      <c r="C137" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" t="s">
+        <v>374</v>
+      </c>
+      <c r="C138" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" t="s">
+        <v>375</v>
+      </c>
+      <c r="C140" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="s">
+        <v>376</v>
+      </c>
+      <c r="C141" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" t="s">
+        <v>377</v>
+      </c>
+      <c r="C142" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" t="s">
+        <v>378</v>
+      </c>
+      <c r="C143" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144" t="s">
+        <v>379</v>
+      </c>
+      <c r="C144" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" t="s">
+        <v>380</v>
+      </c>
+      <c r="C145" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" t="s">
+        <v>381</v>
+      </c>
+      <c r="C146" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>148</v>
+      </c>
+      <c r="B147" t="s">
+        <v>382</v>
+      </c>
+      <c r="C147" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" t="s">
+        <v>383</v>
+      </c>
+      <c r="C148" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" t="s">
+        <v>384</v>
+      </c>
+      <c r="C149" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" t="s">
+        <v>369</v>
+      </c>
+      <c r="C150" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" t="s">
+        <v>328</v>
+      </c>
+      <c r="C151" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152" t="s">
+        <v>385</v>
+      </c>
+      <c r="C152" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" t="s">
+        <v>386</v>
+      </c>
+      <c r="C153" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" t="s">
+        <v>387</v>
+      </c>
+      <c r="C154" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" t="s">
+        <v>388</v>
+      </c>
+      <c r="C155" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s">
+        <v>357</v>
+      </c>
+      <c r="C156" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B157" t="s">
+        <v>334</v>
+      </c>
+      <c r="C157" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>159</v>
+      </c>
+      <c r="B158" t="s">
+        <v>389</v>
+      </c>
+      <c r="C158" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>160</v>
+      </c>
+      <c r="B159" t="s">
+        <v>390</v>
+      </c>
+      <c r="C159" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160" t="s">
+        <v>391</v>
+      </c>
+      <c r="C160" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>162</v>
+      </c>
+      <c r="B161" t="s">
+        <v>392</v>
+      </c>
+      <c r="C161" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162" t="s">
+        <v>393</v>
+      </c>
+      <c r="C162" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
+        <v>164</v>
+      </c>
+      <c r="B163" t="s">
+        <v>394</v>
+      </c>
+      <c r="C163" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164" t="s">
+        <v>395</v>
+      </c>
+      <c r="C164" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
+        <v>166</v>
+      </c>
+      <c r="B165" t="s">
+        <v>396</v>
+      </c>
+      <c r="C165" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>167</v>
+      </c>
+      <c r="B166" t="s">
+        <v>397</v>
+      </c>
+      <c r="C166" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167" t="s">
+        <v>397</v>
+      </c>
+      <c r="C167" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168" t="s">
+        <v>398</v>
+      </c>
+      <c r="C168" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169" t="s">
+        <v>399</v>
+      </c>
+      <c r="C169" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
+        <v>172</v>
+      </c>
+      <c r="B171" t="s">
+        <v>344</v>
+      </c>
+      <c r="C171" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172" t="s">
+        <v>299</v>
+      </c>
+      <c r="C172" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
+        <v>174</v>
+      </c>
+      <c r="B173" t="s">
+        <v>400</v>
+      </c>
+      <c r="C173" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174" t="s">
+        <v>401</v>
+      </c>
+      <c r="C174" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175" t="s">
+        <v>402</v>
+      </c>
+      <c r="C175" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176" t="s">
+        <v>403</v>
+      </c>
+      <c r="C176" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" t="s">
+        <v>404</v>
+      </c>
+      <c r="C177" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178" t="s">
+        <v>311</v>
+      </c>
+      <c r="C178" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179" t="s">
+        <v>405</v>
+      </c>
+      <c r="C179" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" t="s">
+        <v>406</v>
+      </c>
+      <c r="C180" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181" t="s">
+        <v>407</v>
+      </c>
+      <c r="C181" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
+        <v>183</v>
+      </c>
+      <c r="B182" t="s">
+        <v>408</v>
+      </c>
+      <c r="C182" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183" t="s">
+        <v>278</v>
+      </c>
+      <c r="C183" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
+        <v>185</v>
+      </c>
+      <c r="B184" t="s">
+        <v>342</v>
+      </c>
+      <c r="C184" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
+        <v>186</v>
+      </c>
+      <c r="B185" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
+        <v>187</v>
+      </c>
+      <c r="B186" t="s">
+        <v>410</v>
+      </c>
+      <c r="C186" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
+        <v>188</v>
+      </c>
+      <c r="B187" t="s">
+        <v>273</v>
+      </c>
+      <c r="C187" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
+        <v>189</v>
+      </c>
+      <c r="B188" t="s">
+        <v>411</v>
+      </c>
+      <c r="C188" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
+        <v>190</v>
+      </c>
+      <c r="B189" t="s">
+        <v>412</v>
+      </c>
+      <c r="C189" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
+        <v>191</v>
+      </c>
+      <c r="B190" t="s">
+        <v>413</v>
+      </c>
+      <c r="C190" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
+        <v>192</v>
+      </c>
+      <c r="B191" t="s">
+        <v>414</v>
+      </c>
+      <c r="C191" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>193</v>
+      </c>
+      <c r="B192" t="s">
+        <v>415</v>
+      </c>
+      <c r="C192" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="B193" t="s">
+        <v>416</v>
+      </c>
+      <c r="C193" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
+        <v>195</v>
+      </c>
+      <c r="B194" t="s">
+        <v>417</v>
+      </c>
+      <c r="C194" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
+        <v>196</v>
+      </c>
+      <c r="B195" t="s">
+        <v>418</v>
+      </c>
+      <c r="C195" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
+        <v>197</v>
+      </c>
+      <c r="B196" t="s">
+        <v>300</v>
+      </c>
+      <c r="C196" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
+        <v>198</v>
+      </c>
+      <c r="B197" t="s">
+        <v>419</v>
+      </c>
+      <c r="C197" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
+        <v>199</v>
+      </c>
+      <c r="B198" t="s">
+        <v>420</v>
+      </c>
+      <c r="C198" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
+        <v>200</v>
+      </c>
+      <c r="B199" t="s">
+        <v>421</v>
+      </c>
+      <c r="C199" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
+        <v>201</v>
+      </c>
+      <c r="B200" t="s">
+        <v>422</v>
+      </c>
+      <c r="C200" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
+        <v>202</v>
+      </c>
+      <c r="B201" t="s">
+        <v>423</v>
+      </c>
+      <c r="C201" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
+        <v>203</v>
+      </c>
+      <c r="B202" t="s">
+        <v>424</v>
+      </c>
+      <c r="C202" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
+        <v>204</v>
+      </c>
+      <c r="B203" t="s">
+        <v>390</v>
+      </c>
+      <c r="C203" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
+        <v>205</v>
+      </c>
+      <c r="B204" t="s">
+        <v>275</v>
+      </c>
+      <c r="C204" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
+        <v>206</v>
+      </c>
+      <c r="B205" t="s">
+        <v>425</v>
+      </c>
+      <c r="C205" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
+        <v>207</v>
+      </c>
+      <c r="B206" t="s">
+        <v>426</v>
+      </c>
+      <c r="C206" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
+        <v>208</v>
+      </c>
+      <c r="B207" t="s">
+        <v>427</v>
+      </c>
+      <c r="C207" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
+        <v>209</v>
+      </c>
+      <c r="B208" t="s">
+        <v>400</v>
+      </c>
+      <c r="C208" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209" t="s">
+        <v>428</v>
+      </c>
+      <c r="C209" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" t="s">
+        <v>211</v>
+      </c>
+      <c r="B210" t="s">
+        <v>429</v>
+      </c>
+      <c r="C210" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
+        <v>212</v>
+      </c>
+      <c r="B211" t="s">
+        <v>430</v>
+      </c>
+      <c r="C211" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" t="s">
+        <v>213</v>
+      </c>
+      <c r="B212" t="s">
+        <v>431</v>
+      </c>
+      <c r="C212" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" t="s">
+        <v>214</v>
+      </c>
+      <c r="B213" t="s">
+        <v>432</v>
+      </c>
+      <c r="C213" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" t="s">
+        <v>215</v>
+      </c>
+      <c r="B214" t="s">
+        <v>433</v>
+      </c>
+      <c r="C214" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215" t="s">
+        <v>434</v>
+      </c>
+      <c r="C215" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+      <c r="B216" t="s">
+        <v>327</v>
+      </c>
+      <c r="C216" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+      <c r="B217" t="s">
+        <v>435</v>
+      </c>
+      <c r="C217" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+      <c r="B218" t="s">
+        <v>349</v>
+      </c>
+      <c r="C218" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+      <c r="B219" t="s">
+        <v>436</v>
+      </c>
+      <c r="C219" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+      <c r="B220" t="s">
+        <v>437</v>
+      </c>
+      <c r="C220" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+      <c r="B221" t="s">
+        <v>438</v>
+      </c>
+      <c r="C221" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+      <c r="B222" t="s">
+        <v>313</v>
+      </c>
+      <c r="C222" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+      <c r="B223" t="s">
+        <v>439</v>
+      </c>
+      <c r="C223" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>225</v>
+      </c>
+      <c r="B224" t="s">
+        <v>440</v>
+      </c>
+      <c r="C224" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
+        <v>226</v>
+      </c>
+      <c r="B225" t="s">
+        <v>421</v>
+      </c>
+      <c r="C225" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
+        <v>227</v>
+      </c>
+      <c r="B226" t="s">
+        <v>441</v>
+      </c>
+      <c r="C226" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" t="s">
+        <v>228</v>
+      </c>
+      <c r="B227" t="s">
+        <v>346</v>
+      </c>
+      <c r="C227" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" t="s">
+        <v>229</v>
+      </c>
+      <c r="B228" t="s">
+        <v>442</v>
+      </c>
+      <c r="C228" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
+        <v>230</v>
+      </c>
+      <c r="B229" t="s">
+        <v>443</v>
+      </c>
+      <c r="C229" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
+        <v>231</v>
+      </c>
+      <c r="B230" t="s">
+        <v>444</v>
+      </c>
+      <c r="C230" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" t="s">
+        <v>232</v>
+      </c>
+      <c r="B231" t="s">
+        <v>445</v>
+      </c>
+      <c r="C231" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>233</v>
+      </c>
+      <c r="B232" t="s">
+        <v>446</v>
+      </c>
+      <c r="C232" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>234</v>
+      </c>
+      <c r="B233" t="s">
+        <v>447</v>
+      </c>
+      <c r="C233" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
+        <v>235</v>
+      </c>
+      <c r="B234" t="s">
+        <v>448</v>
+      </c>
+      <c r="C234" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
+        <v>236</v>
+      </c>
+      <c r="B235" t="s">
+        <v>449</v>
+      </c>
+      <c r="C235" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>237</v>
+      </c>
+      <c r="B236" t="s">
+        <v>450</v>
+      </c>
+      <c r="C236" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
+        <v>238</v>
+      </c>
+      <c r="B237" t="s">
+        <v>451</v>
+      </c>
+      <c r="C237" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238" t="s">
+        <v>452</v>
+      </c>
+      <c r="C238" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
+        <v>240</v>
+      </c>
+      <c r="B239" t="s">
+        <v>412</v>
+      </c>
+      <c r="C239" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
+        <v>241</v>
+      </c>
+      <c r="B240" t="s">
+        <v>453</v>
+      </c>
+      <c r="C240" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" t="s">
+        <v>242</v>
+      </c>
+      <c r="B241" t="s">
+        <v>437</v>
+      </c>
+      <c r="C241" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
+        <v>243</v>
+      </c>
+      <c r="B242" t="s">
+        <v>454</v>
+      </c>
+      <c r="C242" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" t="s">
+        <v>244</v>
+      </c>
+      <c r="B243" t="s">
+        <v>332</v>
+      </c>
+      <c r="C243" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" t="s">
+        <v>245</v>
+      </c>
+      <c r="B244" t="s">
+        <v>455</v>
+      </c>
+      <c r="C244" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
+        <v>246</v>
+      </c>
+      <c r="B245" t="s">
+        <v>456</v>
+      </c>
+      <c r="C245" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" t="s">
+        <v>247</v>
+      </c>
+      <c r="B246" t="s">
+        <v>366</v>
+      </c>
+      <c r="C246" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" t="s">
+        <v>248</v>
+      </c>
+      <c r="B247" t="s">
+        <v>457</v>
+      </c>
+      <c r="C247" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
+        <v>249</v>
+      </c>
+      <c r="B248" t="s">
+        <v>458</v>
+      </c>
+      <c r="C248" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
